--- a/log_procurement.xlsx
+++ b/log_procurement.xlsx
@@ -486,12 +486,6 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D2"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -531,16 +525,6 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H56"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2078,7 +2062,37 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:AB4"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="11" max="11" width="20.83203125" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="13" max="13" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
+    <col min="17" max="17" width="20.83203125" customWidth="1"/>
+    <col min="18" max="18" width="20.83203125" customWidth="1"/>
+    <col min="19" max="19" width="20.83203125" customWidth="1"/>
+    <col min="20" max="20" width="20.83203125" customWidth="1"/>
+    <col min="21" max="21" width="20.83203125" customWidth="1"/>
+    <col min="22" max="22" width="20.83203125" customWidth="1"/>
+    <col min="23" max="23" width="20.83203125" customWidth="1"/>
+    <col min="24" max="24" width="20.83203125" customWidth="1"/>
+    <col min="25" max="25" width="20.83203125" customWidth="1"/>
+    <col min="26" max="26" width="20.83203125" customWidth="1"/>
+    <col min="27" max="27" width="20.83203125" customWidth="1"/>
+    <col min="28" max="28" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2118,37 +2132,52 @@
         <v>EndDate</v>
       </c>
       <c r="M1" t="str">
+        <v>WeeklyEstimatedTonnes</v>
+      </c>
+      <c r="N1" t="str">
         <v>Status</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>AcceptanceDate</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>AcceptanceTime</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>AcceptanceMethod</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>AcceptedByPerson</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>AcceptanceNotes</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
+        <v>LogSpecFileID</v>
+      </c>
+      <c r="U1" t="str">
+        <v>LogSpecFileName</v>
+      </c>
+      <c r="V1" t="str">
+        <v>LogSpecFileType</v>
+      </c>
+      <c r="W1" t="str">
         <v>Notes</v>
       </c>
-      <c r="T1" t="str">
+      <c r="X1" t="str">
         <v>CreatedBy</v>
       </c>
-      <c r="U1" t="str">
+      <c r="Y1" t="str">
         <v>CreatedDate</v>
       </c>
-      <c r="V1" t="str">
+      <c r="Z1" t="str">
         <v>ChangedBy</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AA1" t="str">
         <v>ChangedDate</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>ForceWeeklyForecast</v>
       </c>
     </row>
     <row r="2">
@@ -2158,10 +2187,10 @@
       <c r="B2" t="str">
         <v>PROC-0001</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
+      <c r="C2" t="str">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
         <v>1</v>
       </c>
       <c r="E2" t="str">
@@ -2173,11 +2202,14 @@
       <c r="G2" t="str">
         <v>PLANTATION</v>
       </c>
+      <c r="H2" t="str">
+        <v>Radiata Pine</v>
+      </c>
       <c r="I2" t="str">
-        <v>KLJ</v>
+        <v/>
       </c>
       <c r="J2" t="str">
-        <v>LKJ</v>
+        <v/>
       </c>
       <c r="K2" t="str">
         <v>ASDA</v>
@@ -2186,37 +2218,52 @@
         <v>SAD</v>
       </c>
       <c r="M2" t="str">
-        <v>Draft</v>
+        <v/>
       </c>
       <c r="N2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="O2" t="str">
         <v>SDA</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>SA</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <v>In Person</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="R2" t="str">
         <v>SAD</v>
-      </c>
-      <c r="R2" t="str">
-        <v>ASD</v>
       </c>
       <c r="S2" t="str">
         <v>ASD</v>
       </c>
       <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
+        <v>ASD</v>
+      </c>
+      <c r="X2" t="str">
         <v>Current User</v>
       </c>
-      <c r="U2" t="str">
+      <c r="Y2" t="str">
         <v>2026-09-15 00:52:10</v>
       </c>
-      <c r="V2" t="str">
+      <c r="Z2" t="str">
         <v>Current User</v>
       </c>
-      <c r="W2" t="str">
-        <v>2026-09-15 00:52:10</v>
+      <c r="AA2" t="str">
+        <v>2026-09-25 08:31:30</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2226,10 +2273,10 @@
       <c r="B3" t="str">
         <v>PROC-0002</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
+      <c r="C3" t="str">
+        <v>1</v>
+      </c>
+      <c r="D3" t="str">
         <v>1</v>
       </c>
       <c r="E3" t="str">
@@ -2241,11 +2288,14 @@
       <c r="G3" t="str">
         <v>SDF</v>
       </c>
+      <c r="H3" t="str">
+        <v>Radiata Pine</v>
+      </c>
       <c r="I3" t="str">
-        <v>SDFSD</v>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <v>SF</v>
+        <v/>
       </c>
       <c r="K3" t="str">
         <v>SF</v>
@@ -2254,51 +2304,164 @@
         <v>DSF</v>
       </c>
       <c r="M3" t="str">
-        <v>Draft</v>
+        <v/>
       </c>
       <c r="N3" t="str">
+        <v>Active</v>
+      </c>
+      <c r="O3" t="str">
         <v>GFH</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>HGF</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <v>Phone</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="R3" t="str">
         <v>GFH</v>
       </c>
-      <c r="R3" t="str">
+      <c r="S3" t="str">
         <v>GHF</v>
       </c>
-      <c r="S3" t="str">
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
         <v>FGH</v>
       </c>
-      <c r="T3" t="str">
+      <c r="X3" t="str">
         <v>Current User</v>
       </c>
-      <c r="U3" t="str">
+      <c r="Y3" t="str">
         <v>2026-09-15 00:54:11</v>
       </c>
-      <c r="V3" t="str">
+      <c r="Z3" t="str">
         <v>Current User</v>
       </c>
-      <c r="W3" t="str">
-        <v>2026-09-15 00:54:11</v>
+      <c r="AA3" t="str">
+        <v>2026-09-25 08:31:05</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>HVP-0001</v>
+      </c>
+      <c r="C4" t="str">
+        <v>1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>1</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Coupe</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>Radiata Pine</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4">
+        <v>3300</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Active</v>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v>In Person</v>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v>Current User</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>2026-09-25 08:24:22</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>Current User</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>2026-09-25 08:24:22</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W3"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:W3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L5"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="11" max="11" width="20.83203125" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2323,119 +2486,176 @@
         <v>AgreedPricePerTonne</v>
       </c>
       <c r="H1" t="str">
+        <v>ResalePrice</v>
+      </c>
+      <c r="I1" t="str">
         <v>AgreedTonnes</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>DeliveredTonnes</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>RemainingTonnes</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Notes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="str">
-        <v>PROC-0001</v>
+        <v>HVP-0001</v>
       </c>
       <c r="C2" t="str">
         <v>Radiata Pine</v>
       </c>
       <c r="D2" t="str">
-        <v>Fresh Logs</v>
+        <v>Green</v>
       </c>
       <c r="E2" t="str">
-        <v>K</v>
+        <v>A</v>
       </c>
       <c r="F2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>3000</v>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="str">
-        <v>PROC-0001</v>
+        <v>PROC-0002</v>
       </c>
       <c r="C3" t="str">
         <v>Radiata Pine</v>
       </c>
       <c r="D3" t="str">
-        <v>Fresh Logs</v>
+        <v>Green</v>
       </c>
       <c r="E3" t="str">
-        <v>KI</v>
+        <v>A</v>
       </c>
       <c r="F3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I3">
+        <v>5000</v>
+      </c>
+      <c r="J3">
         <v>0</v>
       </c>
-      <c r="J3">
-        <v>2000</v>
+      <c r="K3">
+        <v>5000</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>PROC-0002</v>
+        <v>PROC-0001</v>
       </c>
       <c r="C4" t="str">
         <v>Radiata Pine</v>
       </c>
       <c r="D4" t="str">
-        <v>Fresh Logs</v>
+        <v>Green</v>
       </c>
       <c r="E4" t="str">
-        <v>Pulp</v>
+        <v>K</v>
       </c>
       <c r="F4">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G4">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H4">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="I4">
+        <v>3000</v>
+      </c>
+      <c r="J4">
         <v>0</v>
       </c>
-      <c r="J4">
-        <v>5000</v>
+      <c r="K4">
+        <v>3000</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>PROC-0001</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Radiata Pine</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Green</v>
+      </c>
+      <c r="E5" t="str">
+        <v>A</v>
+      </c>
+      <c r="F5">
+        <v>60</v>
+      </c>
+      <c r="G5">
+        <v>60</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>2000</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>2000</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
